--- a/Projects/Pistons-Lineup-Data-2024-25.xlsx
+++ b/Projects/Pistons-Lineup-Data-2024-25.xlsx
@@ -8,14 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thejjserg/Documents/GitHub/basketball-analytics/Projects/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A930266F-9837-2A4A-82CF-C35BDAF7DC32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D298B982-8C46-6342-B714-5BCFC48F96C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1180" yWindow="900" windowWidth="27960" windowHeight="17180" activeTab="2" xr2:uid="{8C050E1C-C5BA-9F4C-A171-8E53342E2AE2}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17680" activeTab="6" xr2:uid="{8C050E1C-C5BA-9F4C-A171-8E53342E2AE2}"/>
   </bookViews>
   <sheets>
     <sheet name="2-Player All Games Traditional" sheetId="1" r:id="rId1"/>
     <sheet name="2-Player All Games Advanced" sheetId="2" r:id="rId2"/>
     <sheet name="2-Player All Games Scoring" sheetId="3" r:id="rId3"/>
+    <sheet name="5-Player All Games Traditional" sheetId="6" r:id="rId4"/>
+    <sheet name="5-Player All Games Advanced" sheetId="7" r:id="rId5"/>
+    <sheet name="5-Player All Games Scoring" sheetId="5" r:id="rId6"/>
+    <sheet name="Resources" sheetId="8" r:id="rId7"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -38,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="173">
   <si>
     <t>Lineups</t>
   </si>
@@ -526,6 +530,48 @@
   </si>
   <si>
     <t>L. Waters III - B. Klintman</t>
+  </si>
+  <si>
+    <t>T. Harris - T. Hardaway Jr. - C. Cunningham - J. Duren - A. Thompson</t>
+  </si>
+  <si>
+    <t>T. Harris - T. Hardaway Jr. - C. Cunningham - J. Ivey - J. Duren</t>
+  </si>
+  <si>
+    <t>D. Schröder - M. Beasley - I. Stewart - S. Fontecchio - R. Holland II</t>
+  </si>
+  <si>
+    <t>M. Beasley - I. Stewart - M. Sasser - S. Fontecchio - R. Holland II</t>
+  </si>
+  <si>
+    <t>T. Harris - M. Beasley - C. Cunningham - J. Ivey - J. Duren</t>
+  </si>
+  <si>
+    <t>T. Harris - T. Hardaway Jr. - M. Beasley - C. Cunningham - J. Duren</t>
+  </si>
+  <si>
+    <t>M. Beasley - I. Stewart - J. Ivey - S. Fontecchio - R. Holland II</t>
+  </si>
+  <si>
+    <t>M. Beasley - I. Stewart - C. Cunningham - S. Fontecchio - R. Holland II</t>
+  </si>
+  <si>
+    <t>T. Harris - M. Beasley - C. Cunningham - J. Duren - A. Thompson</t>
+  </si>
+  <si>
+    <t>T. Harris - T. Hardaway Jr. - M. Beasley - I. Stewart - C. Cunningham</t>
+  </si>
+  <si>
+    <t>T. Harris - D. Schröder - M. Beasley - I. Stewart - S. Fontecchio</t>
+  </si>
+  <si>
+    <t>T. Harris - M. Beasley - I. Stewart - C. Cunningham - S. Fontecchio</t>
+  </si>
+  <si>
+    <t>URL</t>
+  </si>
+  <si>
+    <t>https://www.nba.com/stats/lineups/advanced?CF=GP*GE*15&amp;Season=2024-25&amp;TeamID=1610612765&amp;slug=advanced</t>
   </si>
 </sst>
 </file>
@@ -22869,4 +22915,2781 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C2E36E3-1A62-694B-A7A3-FC1BEF9966F9}">
+  <dimension ref="A1:Y13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="65.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="5.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.83203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.83203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="7" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.83203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="5.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="3">
+        <v>39</v>
+      </c>
+      <c r="D2" s="3">
+        <v>12.6</v>
+      </c>
+      <c r="E2" s="3">
+        <v>31.2</v>
+      </c>
+      <c r="F2" s="4">
+        <v>12.5</v>
+      </c>
+      <c r="G2" s="4">
+        <v>24.6</v>
+      </c>
+      <c r="H2" s="3">
+        <v>50.7</v>
+      </c>
+      <c r="I2" s="4">
+        <v>2.4</v>
+      </c>
+      <c r="J2" s="4">
+        <v>6.9</v>
+      </c>
+      <c r="K2" s="3">
+        <v>35.1</v>
+      </c>
+      <c r="L2" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="M2" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="N2" s="3">
+        <v>74.099999999999994</v>
+      </c>
+      <c r="O2" s="4">
+        <v>3.7</v>
+      </c>
+      <c r="P2" s="4">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="Q2" s="4">
+        <v>12.8</v>
+      </c>
+      <c r="R2" s="4">
+        <v>7.4</v>
+      </c>
+      <c r="S2" s="4">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="T2" s="4">
+        <v>2.5</v>
+      </c>
+      <c r="U2" s="4">
+        <v>1.4</v>
+      </c>
+      <c r="V2" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="W2" s="3">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="X2" s="3">
+        <v>4.5</v>
+      </c>
+      <c r="Y2" s="3">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="3">
+        <v>21</v>
+      </c>
+      <c r="D3" s="3">
+        <v>12.4</v>
+      </c>
+      <c r="E3" s="3">
+        <v>30.2</v>
+      </c>
+      <c r="F3" s="4">
+        <v>11.5</v>
+      </c>
+      <c r="G3" s="4">
+        <v>22.4</v>
+      </c>
+      <c r="H3" s="3">
+        <v>51.4</v>
+      </c>
+      <c r="I3" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="J3" s="4">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="K3" s="3">
+        <v>42.9</v>
+      </c>
+      <c r="L3" s="3">
+        <v>3.4</v>
+      </c>
+      <c r="M3" s="3">
+        <v>4.7</v>
+      </c>
+      <c r="N3" s="3">
+        <v>72.7</v>
+      </c>
+      <c r="O3" s="4">
+        <v>2.9</v>
+      </c>
+      <c r="P3" s="4">
+        <v>8.5</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>11.4</v>
+      </c>
+      <c r="R3" s="4">
+        <v>7.5</v>
+      </c>
+      <c r="S3" s="4">
+        <v>4</v>
+      </c>
+      <c r="T3" s="4">
+        <v>1.2</v>
+      </c>
+      <c r="U3" s="4">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="V3" s="4">
+        <v>1.3</v>
+      </c>
+      <c r="W3" s="3">
+        <v>5</v>
+      </c>
+      <c r="X3" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="Y3" s="3">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="3">
+        <v>17</v>
+      </c>
+      <c r="D4" s="3">
+        <v>5</v>
+      </c>
+      <c r="E4" s="3">
+        <v>12</v>
+      </c>
+      <c r="F4" s="4">
+        <v>3.9</v>
+      </c>
+      <c r="G4" s="4">
+        <v>8.9</v>
+      </c>
+      <c r="H4" s="3">
+        <v>43.4</v>
+      </c>
+      <c r="I4" s="4">
+        <v>1.9</v>
+      </c>
+      <c r="J4" s="4">
+        <v>4.2</v>
+      </c>
+      <c r="K4" s="3">
+        <v>45.1</v>
+      </c>
+      <c r="L4" s="3">
+        <v>2.4</v>
+      </c>
+      <c r="M4" s="3">
+        <v>2.7</v>
+      </c>
+      <c r="N4" s="3">
+        <v>87</v>
+      </c>
+      <c r="O4" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="P4" s="4">
+        <v>3.9</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>4.8</v>
+      </c>
+      <c r="R4" s="4">
+        <v>3</v>
+      </c>
+      <c r="S4" s="4">
+        <v>1.6</v>
+      </c>
+      <c r="T4" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="U4" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="V4" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="W4" s="3">
+        <v>2.8</v>
+      </c>
+      <c r="X4" s="3">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="Y4" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="3">
+        <v>25</v>
+      </c>
+      <c r="D5" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="E5" s="3">
+        <v>9.9</v>
+      </c>
+      <c r="F5" s="4">
+        <v>3.4</v>
+      </c>
+      <c r="G5" s="4">
+        <v>7.3</v>
+      </c>
+      <c r="H5" s="3">
+        <v>47</v>
+      </c>
+      <c r="I5" s="4">
+        <v>1.8</v>
+      </c>
+      <c r="J5" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="K5" s="3">
+        <v>48.4</v>
+      </c>
+      <c r="L5" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="M5" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="N5" s="3">
+        <v>76.3</v>
+      </c>
+      <c r="O5" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="P5" s="4">
+        <v>2.8</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>3.6</v>
+      </c>
+      <c r="R5" s="4">
+        <v>2.5</v>
+      </c>
+      <c r="S5" s="4">
+        <v>1.6</v>
+      </c>
+      <c r="T5" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="U5" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="V5" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="W5" s="3">
+        <v>1.9</v>
+      </c>
+      <c r="X5" s="3">
+        <v>1.4</v>
+      </c>
+      <c r="Y5" s="3">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="3">
+        <v>15</v>
+      </c>
+      <c r="D6" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="E6" s="3">
+        <v>10.1</v>
+      </c>
+      <c r="F6" s="4">
+        <v>3.6</v>
+      </c>
+      <c r="G6" s="4">
+        <v>7.3</v>
+      </c>
+      <c r="H6" s="3">
+        <v>49.5</v>
+      </c>
+      <c r="I6" s="4">
+        <v>1.3</v>
+      </c>
+      <c r="J6" s="4">
+        <v>3.1</v>
+      </c>
+      <c r="K6" s="3">
+        <v>41.3</v>
+      </c>
+      <c r="L6" s="3">
+        <v>1.6</v>
+      </c>
+      <c r="M6" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="N6" s="3">
+        <v>75</v>
+      </c>
+      <c r="O6" s="4">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="P6" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="R6" s="4">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="S6" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="T6" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="U6" s="4">
+        <v>1</v>
+      </c>
+      <c r="V6" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="W6" s="3">
+        <v>1.8</v>
+      </c>
+      <c r="X6" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="Y6" s="3">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="3">
+        <v>50</v>
+      </c>
+      <c r="D7" s="3">
+        <v>4</v>
+      </c>
+      <c r="E7" s="3">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="F7" s="4">
+        <v>3.6</v>
+      </c>
+      <c r="G7" s="4">
+        <v>7</v>
+      </c>
+      <c r="H7" s="3">
+        <v>51.6</v>
+      </c>
+      <c r="I7" s="4">
+        <v>1</v>
+      </c>
+      <c r="J7" s="4">
+        <v>2.6</v>
+      </c>
+      <c r="K7" s="3">
+        <v>37.4</v>
+      </c>
+      <c r="L7" s="3">
+        <v>2</v>
+      </c>
+      <c r="M7" s="3">
+        <v>2.4</v>
+      </c>
+      <c r="N7" s="3">
+        <v>83.9</v>
+      </c>
+      <c r="O7" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="P7" s="4">
+        <v>2.8</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="R7" s="4">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="S7" s="4">
+        <v>1.3</v>
+      </c>
+      <c r="T7" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="U7" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="V7" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="W7" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="X7" s="3">
+        <v>1.7</v>
+      </c>
+      <c r="Y7" s="3">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="3">
+        <v>20</v>
+      </c>
+      <c r="D8" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="E8" s="3">
+        <v>8.9</v>
+      </c>
+      <c r="F8" s="4">
+        <v>3.2</v>
+      </c>
+      <c r="G8" s="4">
+        <v>7.2</v>
+      </c>
+      <c r="H8" s="3">
+        <v>44.4</v>
+      </c>
+      <c r="I8" s="4">
+        <v>1.3</v>
+      </c>
+      <c r="J8" s="4">
+        <v>3.3</v>
+      </c>
+      <c r="K8" s="3">
+        <v>40</v>
+      </c>
+      <c r="L8" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="M8" s="3">
+        <v>1.3</v>
+      </c>
+      <c r="N8" s="3">
+        <v>88.5</v>
+      </c>
+      <c r="O8" s="4">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="P8" s="4">
+        <v>2.7</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>3.8</v>
+      </c>
+      <c r="R8" s="4">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="S8" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="T8" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="U8" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="V8" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="W8" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="X8" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="Y8" s="3">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="3">
+        <v>28</v>
+      </c>
+      <c r="D9" s="3">
+        <v>3.3</v>
+      </c>
+      <c r="E9" s="3">
+        <v>7.2</v>
+      </c>
+      <c r="F9" s="4">
+        <v>2.5</v>
+      </c>
+      <c r="G9" s="4">
+        <v>6.6</v>
+      </c>
+      <c r="H9" s="3">
+        <v>38.4</v>
+      </c>
+      <c r="I9" s="4">
+        <v>1</v>
+      </c>
+      <c r="J9" s="4">
+        <v>3.1</v>
+      </c>
+      <c r="K9" s="3">
+        <v>33.700000000000003</v>
+      </c>
+      <c r="L9" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="M9" s="3">
+        <v>1.3</v>
+      </c>
+      <c r="N9" s="3">
+        <v>81.099999999999994</v>
+      </c>
+      <c r="O9" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="P9" s="4">
+        <v>2.6</v>
+      </c>
+      <c r="Q9" s="4">
+        <v>3.4</v>
+      </c>
+      <c r="R9" s="4">
+        <v>1.6</v>
+      </c>
+      <c r="S9" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="T9" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="U9" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="V9" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="W9" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="X9" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="Y9" s="3">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="3">
+        <v>20</v>
+      </c>
+      <c r="D10" s="3">
+        <v>2.8</v>
+      </c>
+      <c r="E10" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="F10" s="4">
+        <v>2.5</v>
+      </c>
+      <c r="G10" s="4">
+        <v>5</v>
+      </c>
+      <c r="H10" s="3">
+        <v>50.5</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="J10" s="4">
+        <v>1.4</v>
+      </c>
+      <c r="K10" s="3">
+        <v>35.700000000000003</v>
+      </c>
+      <c r="L10" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="M10" s="3">
+        <v>0.9</v>
+      </c>
+      <c r="N10" s="3">
+        <v>76.5</v>
+      </c>
+      <c r="O10" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="P10" s="4">
+        <v>1.6</v>
+      </c>
+      <c r="Q10" s="4">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="R10" s="4">
+        <v>1.3</v>
+      </c>
+      <c r="S10" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="T10" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="U10" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="V10" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="W10" s="3">
+        <v>1.3</v>
+      </c>
+      <c r="X10" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="Y10" s="3">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A11" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="3">
+        <v>33</v>
+      </c>
+      <c r="D11" s="3">
+        <v>2.4</v>
+      </c>
+      <c r="E11" s="3">
+        <v>6.1</v>
+      </c>
+      <c r="F11" s="4">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="G11" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="H11" s="3">
+        <v>47.7</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="J11" s="4">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="K11" s="3">
+        <v>40.799999999999997</v>
+      </c>
+      <c r="L11" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="M11" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="N11" s="3">
+        <v>77.099999999999994</v>
+      </c>
+      <c r="O11" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="P11" s="4">
+        <v>1.9</v>
+      </c>
+      <c r="Q11" s="4">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="R11" s="4">
+        <v>1.3</v>
+      </c>
+      <c r="S11" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="T11" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="U11" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="V11" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="W11" s="3">
+        <v>1</v>
+      </c>
+      <c r="X11" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="3">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="3">
+        <v>15</v>
+      </c>
+      <c r="D12" s="3">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="E12" s="3">
+        <v>6</v>
+      </c>
+      <c r="F12" s="4">
+        <v>2.4</v>
+      </c>
+      <c r="G12" s="4">
+        <v>4.5</v>
+      </c>
+      <c r="H12" s="3">
+        <v>53.7</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="J12" s="4">
+        <v>1.9</v>
+      </c>
+      <c r="K12" s="3">
+        <v>41.4</v>
+      </c>
+      <c r="L12" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="M12" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="N12" s="3">
+        <v>66.7</v>
+      </c>
+      <c r="O12" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="P12" s="4">
+        <v>1.9</v>
+      </c>
+      <c r="Q12" s="4">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="R12" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="S12" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="T12" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="U12" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="V12" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="W12" s="3">
+        <v>1.3</v>
+      </c>
+      <c r="X12" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="Y12" s="3">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A13" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="3">
+        <v>25</v>
+      </c>
+      <c r="D13" s="3">
+        <v>1.6</v>
+      </c>
+      <c r="E13" s="3">
+        <v>4.2</v>
+      </c>
+      <c r="F13" s="4">
+        <v>1.6</v>
+      </c>
+      <c r="G13" s="4">
+        <v>2.9</v>
+      </c>
+      <c r="H13" s="3">
+        <v>55.6</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="J13" s="4">
+        <v>1.2</v>
+      </c>
+      <c r="K13" s="3">
+        <v>40</v>
+      </c>
+      <c r="L13" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="M13" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="N13" s="3">
+        <v>70</v>
+      </c>
+      <c r="O13" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="P13" s="4">
+        <v>1.3</v>
+      </c>
+      <c r="Q13" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="R13" s="4">
+        <v>1</v>
+      </c>
+      <c r="S13" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="T13" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="U13" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="V13" s="4">
+        <v>0.3</v>
+      </c>
+      <c r="W13" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="X13" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="Y13" s="3">
+        <v>0.4</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" display="https://www.nba.com/team/1610612765/traditional" xr:uid="{82D66CD0-F5A7-AA45-B781-9DBC916456C2}"/>
+    <hyperlink ref="F2" r:id="rId2" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=FGM&amp;GROUP_ID=-202699-203501-1630595-1631105-1641709-&amp;GameID=&amp;GroupID=-202699-203501-1630595-1631105-1641709-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=3&amp;sct=plot&amp;section=game" xr:uid="{5D90BC6E-7673-C84C-A025-52B20D940D17}"/>
+    <hyperlink ref="G2" r:id="rId3" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=FGA&amp;GROUP_ID=-202699-203501-1630595-1631105-1641709-&amp;GameID=&amp;GroupID=-202699-203501-1630595-1631105-1641709-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=3&amp;sct=plot&amp;section=game" xr:uid="{11BCCEE9-63B3-0748-AF2B-A0CC06DB8218}"/>
+    <hyperlink ref="I2" r:id="rId4" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=FG3M&amp;GROUP_ID=-202699-203501-1630595-1631105-1641709-&amp;GameID=&amp;GroupID=-202699-203501-1630595-1631105-1641709-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=3&amp;sct=plot&amp;section=game" xr:uid="{05DEAE21-F3BA-3B49-9133-7569490C8A4D}"/>
+    <hyperlink ref="J2" r:id="rId5" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=FG3A&amp;GROUP_ID=-202699-203501-1630595-1631105-1641709-&amp;GameID=&amp;GroupID=-202699-203501-1630595-1631105-1641709-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=3&amp;sct=plot&amp;section=game" xr:uid="{3CAE923C-6A37-DC42-9C1A-D8E1FDC902DF}"/>
+    <hyperlink ref="O2" r:id="rId6" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=OREB&amp;GROUP_ID=-202699-203501-1630595-1631105-1641709-&amp;GameID=&amp;GroupID=-202699-203501-1630595-1631105-1641709-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{4638F6FB-7794-FA4E-B59A-7D1B7AEE8D86}"/>
+    <hyperlink ref="P2" r:id="rId7" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=DREB&amp;GROUP_ID=-202699-203501-1630595-1631105-1641709-&amp;GameID=&amp;GroupID=-202699-203501-1630595-1631105-1641709-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{C66140AF-2CC6-F643-B42C-CE15D4E76A8B}"/>
+    <hyperlink ref="Q2" r:id="rId8" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=REB&amp;GROUP_ID=-202699-203501-1630595-1631105-1641709-&amp;GameID=&amp;GroupID=-202699-203501-1630595-1631105-1641709-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{32A46E38-B8F5-BA40-A538-A480B24A967B}"/>
+    <hyperlink ref="R2" r:id="rId9" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=AST&amp;GROUP_ID=-202699-203501-1630595-1631105-1641709-&amp;GameID=&amp;GroupID=-202699-203501-1630595-1631105-1641709-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{199648A1-540B-A64C-99B4-4AA2B129C9D1}"/>
+    <hyperlink ref="S2" r:id="rId10" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=TOV&amp;GROUP_ID=-202699-203501-1630595-1631105-1641709-&amp;GameID=&amp;GroupID=-202699-203501-1630595-1631105-1641709-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{354C9EE5-E209-F947-9614-E7514BB3CE5E}"/>
+    <hyperlink ref="T2" r:id="rId11" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=STL&amp;GROUP_ID=-202699-203501-1630595-1631105-1641709-&amp;GameID=&amp;GroupID=-202699-203501-1630595-1631105-1641709-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{097767F0-803D-E248-BB50-093438B1734E}"/>
+    <hyperlink ref="U2" r:id="rId12" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=BLK&amp;GROUP_ID=-202699-203501-1630595-1631105-1641709-&amp;GameID=&amp;GroupID=-202699-203501-1630595-1631105-1641709-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{61DDF561-C069-A844-B086-2A1625240F11}"/>
+    <hyperlink ref="V2" r:id="rId13" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=BLKA&amp;GROUP_ID=-202699-203501-1630595-1631105-1641709-&amp;GameID=&amp;GroupID=-202699-203501-1630595-1631105-1641709-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{17E2EB61-A767-5C40-A4FA-17D0715E898E}"/>
+    <hyperlink ref="B3" r:id="rId14" display="https://www.nba.com/team/1610612765/traditional" xr:uid="{54EF0543-97B4-4044-9A94-8EF89154D6F2}"/>
+    <hyperlink ref="F3" r:id="rId15" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=FGM&amp;GROUP_ID=-202699-203501-1630595-1631093-1631105-&amp;GameID=&amp;GroupID=-202699-203501-1630595-1631093-1631105-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=3&amp;sct=plot&amp;section=game" xr:uid="{E97017DD-99BC-E747-BED4-5E8213F17839}"/>
+    <hyperlink ref="G3" r:id="rId16" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=FGA&amp;GROUP_ID=-202699-203501-1630595-1631093-1631105-&amp;GameID=&amp;GroupID=-202699-203501-1630595-1631093-1631105-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=3&amp;sct=plot&amp;section=game" xr:uid="{E97B2B0B-F36A-4846-BA0E-836ADA991023}"/>
+    <hyperlink ref="I3" r:id="rId17" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=FG3M&amp;GROUP_ID=-202699-203501-1630595-1631093-1631105-&amp;GameID=&amp;GroupID=-202699-203501-1630595-1631093-1631105-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=3&amp;sct=plot&amp;section=game" xr:uid="{E7F719A9-6187-C446-8DBB-1794076C697B}"/>
+    <hyperlink ref="J3" r:id="rId18" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=FG3A&amp;GROUP_ID=-202699-203501-1630595-1631093-1631105-&amp;GameID=&amp;GroupID=-202699-203501-1630595-1631093-1631105-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=3&amp;sct=plot&amp;section=game" xr:uid="{EE2F30E5-8BE2-FA4E-A370-FBF853EAAE44}"/>
+    <hyperlink ref="O3" r:id="rId19" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=OREB&amp;GROUP_ID=-202699-203501-1630595-1631093-1631105-&amp;GameID=&amp;GroupID=-202699-203501-1630595-1631093-1631105-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{C37956C2-DDFE-2145-8A38-DDB820420D7C}"/>
+    <hyperlink ref="P3" r:id="rId20" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=DREB&amp;GROUP_ID=-202699-203501-1630595-1631093-1631105-&amp;GameID=&amp;GroupID=-202699-203501-1630595-1631093-1631105-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{D7E47F53-ECC9-1947-A534-B790AF816D30}"/>
+    <hyperlink ref="Q3" r:id="rId21" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=REB&amp;GROUP_ID=-202699-203501-1630595-1631093-1631105-&amp;GameID=&amp;GroupID=-202699-203501-1630595-1631093-1631105-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{956782EB-D140-4D49-8C94-5C7608922F97}"/>
+    <hyperlink ref="R3" r:id="rId22" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=AST&amp;GROUP_ID=-202699-203501-1630595-1631093-1631105-&amp;GameID=&amp;GroupID=-202699-203501-1630595-1631093-1631105-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{635DD2BD-2CB7-4A44-8AD1-F41D1B6C0963}"/>
+    <hyperlink ref="S3" r:id="rId23" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=TOV&amp;GROUP_ID=-202699-203501-1630595-1631093-1631105-&amp;GameID=&amp;GroupID=-202699-203501-1630595-1631093-1631105-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{11842A8B-557D-5A40-8A6E-9459659EB5BD}"/>
+    <hyperlink ref="T3" r:id="rId24" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=STL&amp;GROUP_ID=-202699-203501-1630595-1631093-1631105-&amp;GameID=&amp;GroupID=-202699-203501-1630595-1631093-1631105-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{B807BC2E-DDB9-E944-A03D-C4AB10F226D7}"/>
+    <hyperlink ref="U3" r:id="rId25" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=BLK&amp;GROUP_ID=-202699-203501-1630595-1631093-1631105-&amp;GameID=&amp;GroupID=-202699-203501-1630595-1631093-1631105-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{27474F07-310C-3D44-A10B-791B3913EE23}"/>
+    <hyperlink ref="V3" r:id="rId26" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=BLKA&amp;GROUP_ID=-202699-203501-1630595-1631093-1631105-&amp;GameID=&amp;GroupID=-202699-203501-1630595-1631093-1631105-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{139229B4-70D5-034B-BFCC-599419F18484}"/>
+    <hyperlink ref="B4" r:id="rId27" display="https://www.nba.com/team/1610612765/traditional" xr:uid="{EB06C69D-BB3D-8A46-B30B-660EF91A9681}"/>
+    <hyperlink ref="F4" r:id="rId28" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=FGM&amp;GROUP_ID=-203471-1627736-1630191-1631323-1641842-&amp;GameID=&amp;GroupID=-203471-1627736-1630191-1631323-1641842-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=3&amp;sct=plot&amp;section=game" xr:uid="{CBC8A589-9C73-DB4A-B95D-3114B57F7033}"/>
+    <hyperlink ref="G4" r:id="rId29" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=FGA&amp;GROUP_ID=-203471-1627736-1630191-1631323-1641842-&amp;GameID=&amp;GroupID=-203471-1627736-1630191-1631323-1641842-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=3&amp;sct=plot&amp;section=game" xr:uid="{ED327A35-295D-E04F-8A35-8530AFAD0D7D}"/>
+    <hyperlink ref="I4" r:id="rId30" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=FG3M&amp;GROUP_ID=-203471-1627736-1630191-1631323-1641842-&amp;GameID=&amp;GroupID=-203471-1627736-1630191-1631323-1641842-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=3&amp;sct=plot&amp;section=game" xr:uid="{764AE99C-7106-DA4F-9E67-84FC78A64D1D}"/>
+    <hyperlink ref="J4" r:id="rId31" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=FG3A&amp;GROUP_ID=-203471-1627736-1630191-1631323-1641842-&amp;GameID=&amp;GroupID=-203471-1627736-1630191-1631323-1641842-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=3&amp;sct=plot&amp;section=game" xr:uid="{514D9212-ACC6-684D-8546-2CD0FEB32FEC}"/>
+    <hyperlink ref="O4" r:id="rId32" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=OREB&amp;GROUP_ID=-203471-1627736-1630191-1631323-1641842-&amp;GameID=&amp;GroupID=-203471-1627736-1630191-1631323-1641842-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{E5B132E6-4649-B749-ADF1-F5B47390B912}"/>
+    <hyperlink ref="P4" r:id="rId33" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=DREB&amp;GROUP_ID=-203471-1627736-1630191-1631323-1641842-&amp;GameID=&amp;GroupID=-203471-1627736-1630191-1631323-1641842-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{81377C26-DD77-704A-9E4B-2FD37B97E4E3}"/>
+    <hyperlink ref="Q4" r:id="rId34" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=REB&amp;GROUP_ID=-203471-1627736-1630191-1631323-1641842-&amp;GameID=&amp;GroupID=-203471-1627736-1630191-1631323-1641842-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{7B6397F5-1A71-E34B-A1FD-38583BE6A7AD}"/>
+    <hyperlink ref="R4" r:id="rId35" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=AST&amp;GROUP_ID=-203471-1627736-1630191-1631323-1641842-&amp;GameID=&amp;GroupID=-203471-1627736-1630191-1631323-1641842-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{7463EA6B-71CC-1648-826D-53291AD2F7FB}"/>
+    <hyperlink ref="S4" r:id="rId36" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=TOV&amp;GROUP_ID=-203471-1627736-1630191-1631323-1641842-&amp;GameID=&amp;GroupID=-203471-1627736-1630191-1631323-1641842-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{5BA061FF-16A6-6D45-A8B7-0F0A06600FEA}"/>
+    <hyperlink ref="T4" r:id="rId37" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=STL&amp;GROUP_ID=-203471-1627736-1630191-1631323-1641842-&amp;GameID=&amp;GroupID=-203471-1627736-1630191-1631323-1641842-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{E8AF9073-E7AF-304F-AED4-CB554434843A}"/>
+    <hyperlink ref="U4" r:id="rId38" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=BLK&amp;GROUP_ID=-203471-1627736-1630191-1631323-1641842-&amp;GameID=&amp;GroupID=-203471-1627736-1630191-1631323-1641842-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{F49C337D-2166-A94B-8B6A-568EDDEDF286}"/>
+    <hyperlink ref="V4" r:id="rId39" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=BLKA&amp;GROUP_ID=-203471-1627736-1630191-1631323-1641842-&amp;GameID=&amp;GroupID=-203471-1627736-1630191-1631323-1641842-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{5463745F-F06B-2244-BB37-FB4E13347983}"/>
+    <hyperlink ref="B5" r:id="rId40" display="https://www.nba.com/team/1610612765/traditional" xr:uid="{5D70D7D0-38ED-C247-9875-D2C437696AA9}"/>
+    <hyperlink ref="F5" r:id="rId41" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=FGM&amp;GROUP_ID=-1627736-1630191-1631204-1631323-1641842-&amp;GameID=&amp;GroupID=-1627736-1630191-1631204-1631323-1641842-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=3&amp;sct=plot&amp;section=game" xr:uid="{F0070E79-F708-9048-A391-EACB44D28698}"/>
+    <hyperlink ref="G5" r:id="rId42" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=FGA&amp;GROUP_ID=-1627736-1630191-1631204-1631323-1641842-&amp;GameID=&amp;GroupID=-1627736-1630191-1631204-1631323-1641842-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=3&amp;sct=plot&amp;section=game" xr:uid="{B1A259C1-4106-1C4D-860B-5D4514995D70}"/>
+    <hyperlink ref="I5" r:id="rId43" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=FG3M&amp;GROUP_ID=-1627736-1630191-1631204-1631323-1641842-&amp;GameID=&amp;GroupID=-1627736-1630191-1631204-1631323-1641842-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=3&amp;sct=plot&amp;section=game" xr:uid="{52B7CD2E-0EB4-1C46-987B-6AF41CA2B85D}"/>
+    <hyperlink ref="J5" r:id="rId44" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=FG3A&amp;GROUP_ID=-1627736-1630191-1631204-1631323-1641842-&amp;GameID=&amp;GroupID=-1627736-1630191-1631204-1631323-1641842-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=3&amp;sct=plot&amp;section=game" xr:uid="{ED2A0D6D-0B99-BF4B-8219-199023309F10}"/>
+    <hyperlink ref="O5" r:id="rId45" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=OREB&amp;GROUP_ID=-1627736-1630191-1631204-1631323-1641842-&amp;GameID=&amp;GroupID=-1627736-1630191-1631204-1631323-1641842-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{3DFD1142-7F3B-724E-90A9-53F27239BCF7}"/>
+    <hyperlink ref="P5" r:id="rId46" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=DREB&amp;GROUP_ID=-1627736-1630191-1631204-1631323-1641842-&amp;GameID=&amp;GroupID=-1627736-1630191-1631204-1631323-1641842-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{D87511D5-6240-6342-A89E-133A755046BB}"/>
+    <hyperlink ref="Q5" r:id="rId47" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=REB&amp;GROUP_ID=-1627736-1630191-1631204-1631323-1641842-&amp;GameID=&amp;GroupID=-1627736-1630191-1631204-1631323-1641842-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{1019E57E-6EE7-B049-94BC-6989750FC4FC}"/>
+    <hyperlink ref="R5" r:id="rId48" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=AST&amp;GROUP_ID=-1627736-1630191-1631204-1631323-1641842-&amp;GameID=&amp;GroupID=-1627736-1630191-1631204-1631323-1641842-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{705AE982-4C92-2F48-AF82-B7161D9CE552}"/>
+    <hyperlink ref="S5" r:id="rId49" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=TOV&amp;GROUP_ID=-1627736-1630191-1631204-1631323-1641842-&amp;GameID=&amp;GroupID=-1627736-1630191-1631204-1631323-1641842-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{6D60218F-0CFB-C94A-A662-942D836B367A}"/>
+    <hyperlink ref="T5" r:id="rId50" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=STL&amp;GROUP_ID=-1627736-1630191-1631204-1631323-1641842-&amp;GameID=&amp;GroupID=-1627736-1630191-1631204-1631323-1641842-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{B4A1447E-E525-6640-B478-522102A618E5}"/>
+    <hyperlink ref="U5" r:id="rId51" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=BLK&amp;GROUP_ID=-1627736-1630191-1631204-1631323-1641842-&amp;GameID=&amp;GroupID=-1627736-1630191-1631204-1631323-1641842-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{D2F01089-3EF9-3448-BC6C-BF170963426D}"/>
+    <hyperlink ref="V5" r:id="rId52" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=BLKA&amp;GROUP_ID=-1627736-1630191-1631204-1631323-1641842-&amp;GameID=&amp;GroupID=-1627736-1630191-1631204-1631323-1641842-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{65849895-378F-8840-96B1-84C5F765B2E9}"/>
+    <hyperlink ref="B6" r:id="rId53" display="https://www.nba.com/team/1610612765/traditional" xr:uid="{ABDD4309-9041-0348-96FD-9DEE6A04DCDC}"/>
+    <hyperlink ref="F6" r:id="rId54" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=FGM&amp;GROUP_ID=-202699-1627736-1630595-1631093-1631105-&amp;GameID=&amp;GroupID=-202699-1627736-1630595-1631093-1631105-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=3&amp;sct=plot&amp;section=game" xr:uid="{F8EBF1A4-2460-BE4E-AE61-AB2C9866B148}"/>
+    <hyperlink ref="G6" r:id="rId55" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=FGA&amp;GROUP_ID=-202699-1627736-1630595-1631093-1631105-&amp;GameID=&amp;GroupID=-202699-1627736-1630595-1631093-1631105-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=3&amp;sct=plot&amp;section=game" xr:uid="{59C15403-0EA7-1247-B447-97D486D27E10}"/>
+    <hyperlink ref="I6" r:id="rId56" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=FG3M&amp;GROUP_ID=-202699-1627736-1630595-1631093-1631105-&amp;GameID=&amp;GroupID=-202699-1627736-1630595-1631093-1631105-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=3&amp;sct=plot&amp;section=game" xr:uid="{37FD0C0F-737F-ED43-AD9F-2FA2DDCE290C}"/>
+    <hyperlink ref="J6" r:id="rId57" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=FG3A&amp;GROUP_ID=-202699-1627736-1630595-1631093-1631105-&amp;GameID=&amp;GroupID=-202699-1627736-1630595-1631093-1631105-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=3&amp;sct=plot&amp;section=game" xr:uid="{F44C91B1-94C4-A14E-9D8B-BC25AED5B898}"/>
+    <hyperlink ref="O6" r:id="rId58" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=OREB&amp;GROUP_ID=-202699-1627736-1630595-1631093-1631105-&amp;GameID=&amp;GroupID=-202699-1627736-1630595-1631093-1631105-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{8A64E29D-C883-0D40-944A-B5178513931F}"/>
+    <hyperlink ref="P6" r:id="rId59" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=DREB&amp;GROUP_ID=-202699-1627736-1630595-1631093-1631105-&amp;GameID=&amp;GroupID=-202699-1627736-1630595-1631093-1631105-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{D4B7EF37-8B75-DA4B-96EC-B10003606700}"/>
+    <hyperlink ref="Q6" r:id="rId60" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=REB&amp;GROUP_ID=-202699-1627736-1630595-1631093-1631105-&amp;GameID=&amp;GroupID=-202699-1627736-1630595-1631093-1631105-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{4A4466E0-3D1A-8148-9EEA-F071ED36BC27}"/>
+    <hyperlink ref="R6" r:id="rId61" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=AST&amp;GROUP_ID=-202699-1627736-1630595-1631093-1631105-&amp;GameID=&amp;GroupID=-202699-1627736-1630595-1631093-1631105-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{A3647C83-9515-B347-9EE1-00B41F29E8D1}"/>
+    <hyperlink ref="S6" r:id="rId62" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=TOV&amp;GROUP_ID=-202699-1627736-1630595-1631093-1631105-&amp;GameID=&amp;GroupID=-202699-1627736-1630595-1631093-1631105-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{3A697E4F-AD15-5E47-A1EE-DFE06B13B3B2}"/>
+    <hyperlink ref="T6" r:id="rId63" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=STL&amp;GROUP_ID=-202699-1627736-1630595-1631093-1631105-&amp;GameID=&amp;GroupID=-202699-1627736-1630595-1631093-1631105-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{5A82115F-1057-2145-AC96-EBCEA35B02F4}"/>
+    <hyperlink ref="U6" r:id="rId64" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=BLK&amp;GROUP_ID=-202699-1627736-1630595-1631093-1631105-&amp;GameID=&amp;GroupID=-202699-1627736-1630595-1631093-1631105-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{16EF1E37-FC13-4F4E-98F3-77E65519AB2E}"/>
+    <hyperlink ref="V6" r:id="rId65" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=BLKA&amp;GROUP_ID=-202699-1627736-1630595-1631093-1631105-&amp;GameID=&amp;GroupID=-202699-1627736-1630595-1631093-1631105-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{F32FBA1D-B8A6-7440-A7C7-2284880AB8F8}"/>
+    <hyperlink ref="B7" r:id="rId66" display="https://www.nba.com/team/1610612765/traditional" xr:uid="{109FD2CE-C2AC-304B-BB2F-F2FDB45DC59A}"/>
+    <hyperlink ref="F7" r:id="rId67" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=FGM&amp;GROUP_ID=-202699-203501-1627736-1630595-1631105-&amp;GameID=&amp;GroupID=-202699-203501-1627736-1630595-1631105-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=3&amp;sct=plot&amp;section=game" xr:uid="{D35CECEC-4C4F-9A40-BF8D-3ADE4EFAD566}"/>
+    <hyperlink ref="G7" r:id="rId68" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=FGA&amp;GROUP_ID=-202699-203501-1627736-1630595-1631105-&amp;GameID=&amp;GroupID=-202699-203501-1627736-1630595-1631105-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=3&amp;sct=plot&amp;section=game" xr:uid="{F4E1FE6B-ACCF-224C-8A65-FABCC5EC94B1}"/>
+    <hyperlink ref="I7" r:id="rId69" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=FG3M&amp;GROUP_ID=-202699-203501-1627736-1630595-1631105-&amp;GameID=&amp;GroupID=-202699-203501-1627736-1630595-1631105-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=3&amp;sct=plot&amp;section=game" xr:uid="{DEDDE2AA-F771-0544-A9E4-14FEDF767953}"/>
+    <hyperlink ref="J7" r:id="rId70" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=FG3A&amp;GROUP_ID=-202699-203501-1627736-1630595-1631105-&amp;GameID=&amp;GroupID=-202699-203501-1627736-1630595-1631105-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=3&amp;sct=plot&amp;section=game" xr:uid="{82184F43-5B0A-3B43-8A5D-643275F2C7E3}"/>
+    <hyperlink ref="O7" r:id="rId71" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=OREB&amp;GROUP_ID=-202699-203501-1627736-1630595-1631105-&amp;GameID=&amp;GroupID=-202699-203501-1627736-1630595-1631105-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{1069F4D1-027B-A04F-BF8A-90F9B05F6DB6}"/>
+    <hyperlink ref="P7" r:id="rId72" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=DREB&amp;GROUP_ID=-202699-203501-1627736-1630595-1631105-&amp;GameID=&amp;GroupID=-202699-203501-1627736-1630595-1631105-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{8C24A059-CBF2-144D-8E53-F4BB26C27737}"/>
+    <hyperlink ref="Q7" r:id="rId73" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=REB&amp;GROUP_ID=-202699-203501-1627736-1630595-1631105-&amp;GameID=&amp;GroupID=-202699-203501-1627736-1630595-1631105-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{CFB4F0E1-D11B-9F43-8864-F24113B4D869}"/>
+    <hyperlink ref="R7" r:id="rId74" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=AST&amp;GROUP_ID=-202699-203501-1627736-1630595-1631105-&amp;GameID=&amp;GroupID=-202699-203501-1627736-1630595-1631105-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{542237A5-DAF6-F74C-9F3B-5A744B548F54}"/>
+    <hyperlink ref="S7" r:id="rId75" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=TOV&amp;GROUP_ID=-202699-203501-1627736-1630595-1631105-&amp;GameID=&amp;GroupID=-202699-203501-1627736-1630595-1631105-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{35EDF534-0A4F-8845-B46A-8844A448B755}"/>
+    <hyperlink ref="T7" r:id="rId76" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=STL&amp;GROUP_ID=-202699-203501-1627736-1630595-1631105-&amp;GameID=&amp;GroupID=-202699-203501-1627736-1630595-1631105-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{F925EF08-32D6-164B-8DB4-92482AFA694F}"/>
+    <hyperlink ref="U7" r:id="rId77" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=BLK&amp;GROUP_ID=-202699-203501-1627736-1630595-1631105-&amp;GameID=&amp;GroupID=-202699-203501-1627736-1630595-1631105-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{23B1453E-4C16-1E45-BD12-00848C1D57AF}"/>
+    <hyperlink ref="V7" r:id="rId78" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=BLKA&amp;GROUP_ID=-202699-203501-1627736-1630595-1631105-&amp;GameID=&amp;GroupID=-202699-203501-1627736-1630595-1631105-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{F2CC7E1E-0875-5442-967C-4A25A2E40010}"/>
+    <hyperlink ref="B8" r:id="rId79" display="https://www.nba.com/team/1610612765/traditional" xr:uid="{C523052D-E768-D549-9969-9729C6967D4D}"/>
+    <hyperlink ref="F8" r:id="rId80" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=FGM&amp;GROUP_ID=-1627736-1630191-1631093-1631323-1641842-&amp;GameID=&amp;GroupID=-1627736-1630191-1631093-1631323-1641842-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=3&amp;sct=plot&amp;section=game" xr:uid="{6E725257-9262-1540-A0FD-9CF57F775298}"/>
+    <hyperlink ref="G8" r:id="rId81" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=FGA&amp;GROUP_ID=-1627736-1630191-1631093-1631323-1641842-&amp;GameID=&amp;GroupID=-1627736-1630191-1631093-1631323-1641842-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=3&amp;sct=plot&amp;section=game" xr:uid="{F0E954F8-38C1-C440-BCC1-60951B5C5A81}"/>
+    <hyperlink ref="I8" r:id="rId82" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=FG3M&amp;GROUP_ID=-1627736-1630191-1631093-1631323-1641842-&amp;GameID=&amp;GroupID=-1627736-1630191-1631093-1631323-1641842-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=3&amp;sct=plot&amp;section=game" xr:uid="{A5F8FBA0-397E-9A41-B513-ED4CDE81F183}"/>
+    <hyperlink ref="J8" r:id="rId83" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=FG3A&amp;GROUP_ID=-1627736-1630191-1631093-1631323-1641842-&amp;GameID=&amp;GroupID=-1627736-1630191-1631093-1631323-1641842-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=3&amp;sct=plot&amp;section=game" xr:uid="{CA0BAA78-A711-1845-84C3-8C085F04AC92}"/>
+    <hyperlink ref="O8" r:id="rId84" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=OREB&amp;GROUP_ID=-1627736-1630191-1631093-1631323-1641842-&amp;GameID=&amp;GroupID=-1627736-1630191-1631093-1631323-1641842-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{A8E12FC5-EA17-9143-ABD9-8300422F2DE0}"/>
+    <hyperlink ref="P8" r:id="rId85" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=DREB&amp;GROUP_ID=-1627736-1630191-1631093-1631323-1641842-&amp;GameID=&amp;GroupID=-1627736-1630191-1631093-1631323-1641842-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{365D3A64-1E47-CA45-A472-E2C88BC5362A}"/>
+    <hyperlink ref="Q8" r:id="rId86" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=REB&amp;GROUP_ID=-1627736-1630191-1631093-1631323-1641842-&amp;GameID=&amp;GroupID=-1627736-1630191-1631093-1631323-1641842-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{A48EBCFE-A385-F04C-BDA4-0A92A0AC69EE}"/>
+    <hyperlink ref="R8" r:id="rId87" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=AST&amp;GROUP_ID=-1627736-1630191-1631093-1631323-1641842-&amp;GameID=&amp;GroupID=-1627736-1630191-1631093-1631323-1641842-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{E6245653-53F6-4C46-A466-157FA530AB70}"/>
+    <hyperlink ref="S8" r:id="rId88" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=TOV&amp;GROUP_ID=-1627736-1630191-1631093-1631323-1641842-&amp;GameID=&amp;GroupID=-1627736-1630191-1631093-1631323-1641842-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{DF662C0D-86C0-A547-AC36-7C47F4889852}"/>
+    <hyperlink ref="T8" r:id="rId89" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=STL&amp;GROUP_ID=-1627736-1630191-1631093-1631323-1641842-&amp;GameID=&amp;GroupID=-1627736-1630191-1631093-1631323-1641842-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{0C30F358-E91B-4747-8EDE-8BABD052B110}"/>
+    <hyperlink ref="U8" r:id="rId90" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=BLK&amp;GROUP_ID=-1627736-1630191-1631093-1631323-1641842-&amp;GameID=&amp;GroupID=-1627736-1630191-1631093-1631323-1641842-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{928AEE66-F4D3-1348-914C-54DA702EF727}"/>
+    <hyperlink ref="V8" r:id="rId91" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=BLKA&amp;GROUP_ID=-1627736-1630191-1631093-1631323-1641842-&amp;GameID=&amp;GroupID=-1627736-1630191-1631093-1631323-1641842-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{C0108395-7E2C-5542-A584-D3A6A0326299}"/>
+    <hyperlink ref="B9" r:id="rId92" display="https://www.nba.com/team/1610612765/traditional" xr:uid="{EEAD1FE9-6CCE-AA4E-B52E-422CDD97590C}"/>
+    <hyperlink ref="F9" r:id="rId93" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=FGM&amp;GROUP_ID=-1627736-1630191-1630595-1631323-1641842-&amp;GameID=&amp;GroupID=-1627736-1630191-1630595-1631323-1641842-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=3&amp;sct=plot&amp;section=game" xr:uid="{194C1B04-6BF4-4B40-B8D9-BCA897CE9E2B}"/>
+    <hyperlink ref="G9" r:id="rId94" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=FGA&amp;GROUP_ID=-1627736-1630191-1630595-1631323-1641842-&amp;GameID=&amp;GroupID=-1627736-1630191-1630595-1631323-1641842-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=3&amp;sct=plot&amp;section=game" xr:uid="{39317E5D-BD45-9A41-9F9D-82837C129C64}"/>
+    <hyperlink ref="I9" r:id="rId95" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=FG3M&amp;GROUP_ID=-1627736-1630191-1630595-1631323-1641842-&amp;GameID=&amp;GroupID=-1627736-1630191-1630595-1631323-1641842-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=3&amp;sct=plot&amp;section=game" xr:uid="{8287AB81-45A9-184B-B9E0-F84CF84CEA00}"/>
+    <hyperlink ref="J9" r:id="rId96" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=FG3A&amp;GROUP_ID=-1627736-1630191-1630595-1631323-1641842-&amp;GameID=&amp;GroupID=-1627736-1630191-1630595-1631323-1641842-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=3&amp;sct=plot&amp;section=game" xr:uid="{6014D465-DD62-BD45-A607-2466DFE6763C}"/>
+    <hyperlink ref="O9" r:id="rId97" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=OREB&amp;GROUP_ID=-1627736-1630191-1630595-1631323-1641842-&amp;GameID=&amp;GroupID=-1627736-1630191-1630595-1631323-1641842-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{9F3B0307-A231-1345-A64B-E1867594C47C}"/>
+    <hyperlink ref="P9" r:id="rId98" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=DREB&amp;GROUP_ID=-1627736-1630191-1630595-1631323-1641842-&amp;GameID=&amp;GroupID=-1627736-1630191-1630595-1631323-1641842-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{E1E741B1-0DCC-0D42-AE47-D131B32D3391}"/>
+    <hyperlink ref="Q9" r:id="rId99" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=REB&amp;GROUP_ID=-1627736-1630191-1630595-1631323-1641842-&amp;GameID=&amp;GroupID=-1627736-1630191-1630595-1631323-1641842-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{7B736577-C57F-2540-80AF-7D09998893BE}"/>
+    <hyperlink ref="R9" r:id="rId100" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=AST&amp;GROUP_ID=-1627736-1630191-1630595-1631323-1641842-&amp;GameID=&amp;GroupID=-1627736-1630191-1630595-1631323-1641842-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{D4B4ACA8-AAD3-0D4F-8E2C-EFBA79B5FF66}"/>
+    <hyperlink ref="S9" r:id="rId101" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=TOV&amp;GROUP_ID=-1627736-1630191-1630595-1631323-1641842-&amp;GameID=&amp;GroupID=-1627736-1630191-1630595-1631323-1641842-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{E1A9C7BB-0A50-B240-986B-70DF675DFFFD}"/>
+    <hyperlink ref="T9" r:id="rId102" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=STL&amp;GROUP_ID=-1627736-1630191-1630595-1631323-1641842-&amp;GameID=&amp;GroupID=-1627736-1630191-1630595-1631323-1641842-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{FCAEDA71-1D14-5346-9ED2-DFF13B9EC958}"/>
+    <hyperlink ref="U9" r:id="rId103" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=BLK&amp;GROUP_ID=-1627736-1630191-1630595-1631323-1641842-&amp;GameID=&amp;GroupID=-1627736-1630191-1630595-1631323-1641842-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{DE4D608F-7ADD-D84A-B492-51D32522F53D}"/>
+    <hyperlink ref="V9" r:id="rId104" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=BLKA&amp;GROUP_ID=-1627736-1630191-1630595-1631323-1641842-&amp;GameID=&amp;GroupID=-1627736-1630191-1630595-1631323-1641842-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{639C874B-8EF5-5840-8DAB-C8DD6EE27D5D}"/>
+    <hyperlink ref="B10" r:id="rId105" display="https://www.nba.com/team/1610612765/traditional" xr:uid="{36A61F57-8DCC-E546-B6AF-A7B68AC71CA1}"/>
+    <hyperlink ref="F10" r:id="rId106" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=FGM&amp;GROUP_ID=-202699-1627736-1630595-1631105-1641709-&amp;GameID=&amp;GroupID=-202699-1627736-1630595-1631105-1641709-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=3&amp;sct=plot&amp;section=game" xr:uid="{37D10D0D-1ED7-1D48-BD70-5492AAFAE4A6}"/>
+    <hyperlink ref="G10" r:id="rId107" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=FGA&amp;GROUP_ID=-202699-1627736-1630595-1631105-1641709-&amp;GameID=&amp;GroupID=-202699-1627736-1630595-1631105-1641709-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=3&amp;sct=plot&amp;section=game" xr:uid="{B47C842E-242B-0A40-B43E-F8C49694699B}"/>
+    <hyperlink ref="I10" r:id="rId108" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=FG3M&amp;GROUP_ID=-202699-1627736-1630595-1631105-1641709-&amp;GameID=&amp;GroupID=-202699-1627736-1630595-1631105-1641709-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=3&amp;sct=plot&amp;section=game" xr:uid="{5C3C90EE-B5BF-7B42-93B7-A95F7357CA23}"/>
+    <hyperlink ref="J10" r:id="rId109" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=FG3A&amp;GROUP_ID=-202699-1627736-1630595-1631105-1641709-&amp;GameID=&amp;GroupID=-202699-1627736-1630595-1631105-1641709-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=3&amp;sct=plot&amp;section=game" xr:uid="{0FD36ECA-3B13-774B-9F22-37B81922BFC3}"/>
+    <hyperlink ref="O10" r:id="rId110" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=OREB&amp;GROUP_ID=-202699-1627736-1630595-1631105-1641709-&amp;GameID=&amp;GroupID=-202699-1627736-1630595-1631105-1641709-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{878B9674-546F-7043-9B1B-129EB4425A59}"/>
+    <hyperlink ref="P10" r:id="rId111" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=DREB&amp;GROUP_ID=-202699-1627736-1630595-1631105-1641709-&amp;GameID=&amp;GroupID=-202699-1627736-1630595-1631105-1641709-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{3B0F76C6-900C-4C42-BDE1-EF173330CD81}"/>
+    <hyperlink ref="Q10" r:id="rId112" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=REB&amp;GROUP_ID=-202699-1627736-1630595-1631105-1641709-&amp;GameID=&amp;GroupID=-202699-1627736-1630595-1631105-1641709-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{1FB0EC44-874C-654A-9659-46BC604269EF}"/>
+    <hyperlink ref="R10" r:id="rId113" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=AST&amp;GROUP_ID=-202699-1627736-1630595-1631105-1641709-&amp;GameID=&amp;GroupID=-202699-1627736-1630595-1631105-1641709-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{F743AD6F-537D-DF42-B27C-F6DA7569F765}"/>
+    <hyperlink ref="S10" r:id="rId114" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=TOV&amp;GROUP_ID=-202699-1627736-1630595-1631105-1641709-&amp;GameID=&amp;GroupID=-202699-1627736-1630595-1631105-1641709-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{70CF3A23-E21F-6847-8526-0A8BBDEAF03F}"/>
+    <hyperlink ref="T10" r:id="rId115" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=STL&amp;GROUP_ID=-202699-1627736-1630595-1631105-1641709-&amp;GameID=&amp;GroupID=-202699-1627736-1630595-1631105-1641709-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{101118B2-0B75-0D49-B34F-7DAFF5F57C91}"/>
+    <hyperlink ref="U10" r:id="rId116" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=BLK&amp;GROUP_ID=-202699-1627736-1630595-1631105-1641709-&amp;GameID=&amp;GroupID=-202699-1627736-1630595-1631105-1641709-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{D35FF0C0-C067-994D-8ACE-69385CB6728F}"/>
+    <hyperlink ref="V10" r:id="rId117" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=BLKA&amp;GROUP_ID=-202699-1627736-1630595-1631105-1641709-&amp;GameID=&amp;GroupID=-202699-1627736-1630595-1631105-1641709-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{E14D41AE-4174-CD4D-AE8C-F2F6D4BDA0B9}"/>
+    <hyperlink ref="B11" r:id="rId118" display="https://www.nba.com/team/1610612765/traditional" xr:uid="{869D29FE-CCC4-F048-8E34-415FA1B5D6F3}"/>
+    <hyperlink ref="F11" r:id="rId119" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=FGM&amp;GROUP_ID=-202699-203501-1627736-1630191-1630595-&amp;GameID=&amp;GroupID=-202699-203501-1627736-1630191-1630595-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=3&amp;sct=plot&amp;section=game" xr:uid="{1EA13051-863D-C64B-8C7B-41DE0692E0D8}"/>
+    <hyperlink ref="G11" r:id="rId120" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=FGA&amp;GROUP_ID=-202699-203501-1627736-1630191-1630595-&amp;GameID=&amp;GroupID=-202699-203501-1627736-1630191-1630595-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=3&amp;sct=plot&amp;section=game" xr:uid="{50607BA6-E18B-5045-9B27-3AF9BD13D1A7}"/>
+    <hyperlink ref="I11" r:id="rId121" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=FG3M&amp;GROUP_ID=-202699-203501-1627736-1630191-1630595-&amp;GameID=&amp;GroupID=-202699-203501-1627736-1630191-1630595-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=3&amp;sct=plot&amp;section=game" xr:uid="{ABA2B4D0-491E-0342-9D19-8D0EEF050940}"/>
+    <hyperlink ref="J11" r:id="rId122" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=FG3A&amp;GROUP_ID=-202699-203501-1627736-1630191-1630595-&amp;GameID=&amp;GroupID=-202699-203501-1627736-1630191-1630595-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=3&amp;sct=plot&amp;section=game" xr:uid="{02DBC0BD-52FE-A34F-B9AE-A1E6495D244E}"/>
+    <hyperlink ref="O11" r:id="rId123" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=OREB&amp;GROUP_ID=-202699-203501-1627736-1630191-1630595-&amp;GameID=&amp;GroupID=-202699-203501-1627736-1630191-1630595-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{30F270DB-B719-8849-A081-5B79268712EA}"/>
+    <hyperlink ref="P11" r:id="rId124" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=DREB&amp;GROUP_ID=-202699-203501-1627736-1630191-1630595-&amp;GameID=&amp;GroupID=-202699-203501-1627736-1630191-1630595-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{58E09D17-B83E-4145-9D41-C370AB085AEA}"/>
+    <hyperlink ref="Q11" r:id="rId125" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=REB&amp;GROUP_ID=-202699-203501-1627736-1630191-1630595-&amp;GameID=&amp;GroupID=-202699-203501-1627736-1630191-1630595-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{605CB744-2889-A047-B912-012AEB66FBDA}"/>
+    <hyperlink ref="R11" r:id="rId126" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=AST&amp;GROUP_ID=-202699-203501-1627736-1630191-1630595-&amp;GameID=&amp;GroupID=-202699-203501-1627736-1630191-1630595-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{69D98820-4DF7-714A-831D-483636935C16}"/>
+    <hyperlink ref="S11" r:id="rId127" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=TOV&amp;GROUP_ID=-202699-203501-1627736-1630191-1630595-&amp;GameID=&amp;GroupID=-202699-203501-1627736-1630191-1630595-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{8A7F9365-8DB3-5C43-9373-C64128856A59}"/>
+    <hyperlink ref="T11" r:id="rId128" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=STL&amp;GROUP_ID=-202699-203501-1627736-1630191-1630595-&amp;GameID=&amp;GroupID=-202699-203501-1627736-1630191-1630595-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{C56392CA-E8BE-0B4F-A5DF-ABDD62BE21DE}"/>
+    <hyperlink ref="U11" r:id="rId129" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=BLK&amp;GROUP_ID=-202699-203501-1627736-1630191-1630595-&amp;GameID=&amp;GroupID=-202699-203501-1627736-1630191-1630595-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{FD7A99E8-2793-CA41-B666-17CCC35FD36E}"/>
+    <hyperlink ref="V11" r:id="rId130" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=BLKA&amp;GROUP_ID=-202699-203501-1627736-1630191-1630595-&amp;GameID=&amp;GroupID=-202699-203501-1627736-1630191-1630595-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{E281B0F5-5334-7542-9DAB-689A72D45C9F}"/>
+    <hyperlink ref="B12" r:id="rId131" display="https://www.nba.com/team/1610612765/traditional" xr:uid="{D875EBC2-4955-484D-9C83-FE57B98908A9}"/>
+    <hyperlink ref="F12" r:id="rId132" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=FGM&amp;GROUP_ID=-202699-203471-1627736-1630191-1631323-&amp;GameID=&amp;GroupID=-202699-203471-1627736-1630191-1631323-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=3&amp;sct=plot&amp;section=game" xr:uid="{A7046BE0-F8EE-3545-8B1F-F4C41F30658A}"/>
+    <hyperlink ref="G12" r:id="rId133" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=FGA&amp;GROUP_ID=-202699-203471-1627736-1630191-1631323-&amp;GameID=&amp;GroupID=-202699-203471-1627736-1630191-1631323-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=3&amp;sct=plot&amp;section=game" xr:uid="{7878097E-F8B4-F541-B4EC-182CCBFB9BEB}"/>
+    <hyperlink ref="I12" r:id="rId134" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=FG3M&amp;GROUP_ID=-202699-203471-1627736-1630191-1631323-&amp;GameID=&amp;GroupID=-202699-203471-1627736-1630191-1631323-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=3&amp;sct=plot&amp;section=game" xr:uid="{3969C723-A9E6-FD44-8C34-2025BBDB9552}"/>
+    <hyperlink ref="J12" r:id="rId135" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=FG3A&amp;GROUP_ID=-202699-203471-1627736-1630191-1631323-&amp;GameID=&amp;GroupID=-202699-203471-1627736-1630191-1631323-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=3&amp;sct=plot&amp;section=game" xr:uid="{F90C0F6D-5F7C-1742-BB64-A7E125F3BC2E}"/>
+    <hyperlink ref="O12" r:id="rId136" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=OREB&amp;GROUP_ID=-202699-203471-1627736-1630191-1631323-&amp;GameID=&amp;GroupID=-202699-203471-1627736-1630191-1631323-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{69ABC47A-0044-8345-81E9-AE5C0B8F94B0}"/>
+    <hyperlink ref="P12" r:id="rId137" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=DREB&amp;GROUP_ID=-202699-203471-1627736-1630191-1631323-&amp;GameID=&amp;GroupID=-202699-203471-1627736-1630191-1631323-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{E35865E6-1003-8E44-958D-AAC70DB3EBF9}"/>
+    <hyperlink ref="Q12" r:id="rId138" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=REB&amp;GROUP_ID=-202699-203471-1627736-1630191-1631323-&amp;GameID=&amp;GroupID=-202699-203471-1627736-1630191-1631323-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{7A3A0580-305F-3B4E-B417-AB342EDD4537}"/>
+    <hyperlink ref="R12" r:id="rId139" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=AST&amp;GROUP_ID=-202699-203471-1627736-1630191-1631323-&amp;GameID=&amp;GroupID=-202699-203471-1627736-1630191-1631323-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{74401E65-7122-BA4D-86F0-A8BB1852F936}"/>
+    <hyperlink ref="S12" r:id="rId140" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=TOV&amp;GROUP_ID=-202699-203471-1627736-1630191-1631323-&amp;GameID=&amp;GroupID=-202699-203471-1627736-1630191-1631323-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{95D73AD5-3E54-A64F-95AD-8E97F1ED388F}"/>
+    <hyperlink ref="T12" r:id="rId141" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=STL&amp;GROUP_ID=-202699-203471-1627736-1630191-1631323-&amp;GameID=&amp;GroupID=-202699-203471-1627736-1630191-1631323-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{96691A1D-D4EE-ED4E-8D36-621B5C8BDEB9}"/>
+    <hyperlink ref="U12" r:id="rId142" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=BLK&amp;GROUP_ID=-202699-203471-1627736-1630191-1631323-&amp;GameID=&amp;GroupID=-202699-203471-1627736-1630191-1631323-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{7D882B43-F760-494B-B669-ECBE62216201}"/>
+    <hyperlink ref="V12" r:id="rId143" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=BLKA&amp;GROUP_ID=-202699-203471-1627736-1630191-1631323-&amp;GameID=&amp;GroupID=-202699-203471-1627736-1630191-1631323-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{C2E4ECAA-53EB-6344-9FF2-7DF5A88AC00E}"/>
+    <hyperlink ref="B13" r:id="rId144" display="https://www.nba.com/team/1610612765/traditional" xr:uid="{0037A1B5-FCEB-6A4F-9D4B-9B96FFBE35EB}"/>
+    <hyperlink ref="F13" r:id="rId145" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=FGM&amp;GROUP_ID=-202699-1627736-1630191-1630595-1631323-&amp;GameID=&amp;GroupID=-202699-1627736-1630191-1630595-1631323-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=3&amp;sct=plot&amp;section=game" xr:uid="{624E1346-8101-BF4D-B32F-E0700956CDC3}"/>
+    <hyperlink ref="G13" r:id="rId146" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=FGA&amp;GROUP_ID=-202699-1627736-1630191-1630595-1631323-&amp;GameID=&amp;GroupID=-202699-1627736-1630191-1630595-1631323-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=3&amp;sct=plot&amp;section=game" xr:uid="{252DF2D5-AF1A-9F43-AAC7-67408AF93C70}"/>
+    <hyperlink ref="I13" r:id="rId147" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=FG3M&amp;GROUP_ID=-202699-1627736-1630191-1630595-1631323-&amp;GameID=&amp;GroupID=-202699-1627736-1630191-1630595-1631323-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=3&amp;sct=plot&amp;section=game" xr:uid="{3D064281-7ECF-8544-B9D4-64428AE4B621}"/>
+    <hyperlink ref="J13" r:id="rId148" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=FG3A&amp;GROUP_ID=-202699-1627736-1630191-1630595-1631323-&amp;GameID=&amp;GroupID=-202699-1627736-1630191-1630595-1631323-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=3&amp;sct=plot&amp;section=game" xr:uid="{96B77E5C-725F-4F4A-A0EE-F928351E7DCB}"/>
+    <hyperlink ref="O13" r:id="rId149" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=OREB&amp;GROUP_ID=-202699-1627736-1630191-1630595-1631323-&amp;GameID=&amp;GroupID=-202699-1627736-1630191-1630595-1631323-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{7F96D662-1758-BC43-B679-49337EC6FA5E}"/>
+    <hyperlink ref="P13" r:id="rId150" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=DREB&amp;GROUP_ID=-202699-1627736-1630191-1630595-1631323-&amp;GameID=&amp;GroupID=-202699-1627736-1630191-1630595-1631323-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{672A1554-92D3-BC49-90F4-2EB8AF6F7E48}"/>
+    <hyperlink ref="Q13" r:id="rId151" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=REB&amp;GROUP_ID=-202699-1627736-1630191-1630595-1631323-&amp;GameID=&amp;GroupID=-202699-1627736-1630191-1630595-1631323-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{AAA892B1-62C1-F34B-8168-455948C4C36C}"/>
+    <hyperlink ref="R13" r:id="rId152" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=AST&amp;GROUP_ID=-202699-1627736-1630191-1630595-1631323-&amp;GameID=&amp;GroupID=-202699-1627736-1630191-1630595-1631323-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{EE1CACD7-08DC-1747-8163-2427AD52E76B}"/>
+    <hyperlink ref="S13" r:id="rId153" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=TOV&amp;GROUP_ID=-202699-1627736-1630191-1630595-1631323-&amp;GameID=&amp;GroupID=-202699-1627736-1630191-1630595-1631323-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{D916DA88-0BE6-1941-B83A-868F65C59E63}"/>
+    <hyperlink ref="T13" r:id="rId154" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=STL&amp;GROUP_ID=-202699-1627736-1630191-1630595-1631323-&amp;GameID=&amp;GroupID=-202699-1627736-1630191-1630595-1631323-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{BDF3CD73-1585-2640-9891-4233551C40C8}"/>
+    <hyperlink ref="U13" r:id="rId155" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=BLK&amp;GROUP_ID=-202699-1627736-1630191-1630595-1631323-&amp;GameID=&amp;GroupID=-202699-1627736-1630191-1630595-1631323-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{29AE1911-8390-0C4C-8F51-684747EBC772}"/>
+    <hyperlink ref="V13" r:id="rId156" display="https://www.nba.com/stats/events/?CFID=&amp;CFPARAMS=&amp;ContextMeasure=BLKA&amp;GROUP_ID=-202699-1627736-1630191-1630595-1631323-&amp;GameID=&amp;GroupID=-202699-1627736-1630191-1630595-1631323-&amp;PlayerID=0&amp;Season=2024-25&amp;SeasonType=Regular%20Season&amp;TeamID=1610612765&amp;flag=1&amp;sct=plot&amp;section=game" xr:uid="{0522B18A-3F22-7749-BF1B-0A41CD78F7DF}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E17C941-9702-C041-8F40-560E8978C6FF}">
+  <dimension ref="A1:R13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="65.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="7.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.83203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.83203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="3">
+        <v>39</v>
+      </c>
+      <c r="D2" s="3">
+        <v>491</v>
+      </c>
+      <c r="E2" s="3">
+        <v>115.5</v>
+      </c>
+      <c r="F2" s="3">
+        <v>109.4</v>
+      </c>
+      <c r="G2" s="3">
+        <v>6.1</v>
+      </c>
+      <c r="H2" s="3">
+        <v>59.3</v>
+      </c>
+      <c r="I2" s="3">
+        <v>1.82</v>
+      </c>
+      <c r="J2" s="3">
+        <v>19.100000000000001</v>
+      </c>
+      <c r="K2" s="3">
+        <v>34.700000000000003</v>
+      </c>
+      <c r="L2" s="3">
+        <v>75.900000000000006</v>
+      </c>
+      <c r="M2" s="3">
+        <v>55.5</v>
+      </c>
+      <c r="N2" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="O2" s="3">
+        <v>55.6</v>
+      </c>
+      <c r="P2" s="3">
+        <v>58</v>
+      </c>
+      <c r="Q2" s="3">
+        <v>103.18</v>
+      </c>
+      <c r="R2" s="3">
+        <v>53.7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="3">
+        <v>21</v>
+      </c>
+      <c r="D3" s="3">
+        <v>261</v>
+      </c>
+      <c r="E3" s="3">
+        <v>119.8</v>
+      </c>
+      <c r="F3" s="3">
+        <v>122</v>
+      </c>
+      <c r="G3" s="3">
+        <v>-2.1</v>
+      </c>
+      <c r="H3" s="3">
+        <v>65.3</v>
+      </c>
+      <c r="I3" s="3">
+        <v>1.9</v>
+      </c>
+      <c r="J3" s="3">
+        <v>20.6</v>
+      </c>
+      <c r="K3" s="3">
+        <v>33.200000000000003</v>
+      </c>
+      <c r="L3" s="3">
+        <v>76.2</v>
+      </c>
+      <c r="M3" s="3">
+        <v>55</v>
+      </c>
+      <c r="N3" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="O3" s="3">
+        <v>59.8</v>
+      </c>
+      <c r="P3" s="3">
+        <v>61.7</v>
+      </c>
+      <c r="Q3" s="3">
+        <v>97.66</v>
+      </c>
+      <c r="R3" s="3">
+        <v>48.4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="3">
+        <v>50</v>
+      </c>
+      <c r="D4" s="3">
+        <v>200</v>
+      </c>
+      <c r="E4" s="3">
+        <v>112.6</v>
+      </c>
+      <c r="F4" s="3">
+        <v>116.1</v>
+      </c>
+      <c r="G4" s="3">
+        <v>-3.5</v>
+      </c>
+      <c r="H4" s="3">
+        <v>59.7</v>
+      </c>
+      <c r="I4" s="3">
+        <v>1.64</v>
+      </c>
+      <c r="J4" s="3">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="K4" s="3">
+        <v>23</v>
+      </c>
+      <c r="L4" s="3">
+        <v>77</v>
+      </c>
+      <c r="M4" s="3">
+        <v>50.5</v>
+      </c>
+      <c r="N4" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="O4" s="3">
+        <v>58.5</v>
+      </c>
+      <c r="P4" s="3">
+        <v>63.3</v>
+      </c>
+      <c r="Q4" s="3">
+        <v>107.87</v>
+      </c>
+      <c r="R4" s="3">
+        <v>49.3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="3">
+        <v>25</v>
+      </c>
+      <c r="D5" s="3">
+        <v>103</v>
+      </c>
+      <c r="E5" s="3">
+        <v>109.3</v>
+      </c>
+      <c r="F5" s="3">
+        <v>115.2</v>
+      </c>
+      <c r="G5" s="3">
+        <v>-5.9</v>
+      </c>
+      <c r="H5" s="3">
+        <v>72.099999999999994</v>
+      </c>
+      <c r="I5" s="3">
+        <v>1.55</v>
+      </c>
+      <c r="J5" s="3">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="K5" s="3">
+        <v>29</v>
+      </c>
+      <c r="L5" s="3">
+        <v>66.7</v>
+      </c>
+      <c r="M5" s="3">
+        <v>49.3</v>
+      </c>
+      <c r="N5" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="O5" s="3">
+        <v>59.6</v>
+      </c>
+      <c r="P5" s="3">
+        <v>61.8</v>
+      </c>
+      <c r="Q5" s="3">
+        <v>106.07</v>
+      </c>
+      <c r="R5" s="3">
+        <v>46.4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="3">
+        <v>28</v>
+      </c>
+      <c r="D6" s="3">
+        <v>93</v>
+      </c>
+      <c r="E6" s="3">
+        <v>97.6</v>
+      </c>
+      <c r="F6" s="3">
+        <v>103.4</v>
+      </c>
+      <c r="G6" s="3">
+        <v>-5.9</v>
+      </c>
+      <c r="H6" s="3">
+        <v>63.4</v>
+      </c>
+      <c r="I6" s="3">
+        <v>1.96</v>
+      </c>
+      <c r="J6" s="3">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="K6" s="3">
+        <v>24.6</v>
+      </c>
+      <c r="L6" s="3">
+        <v>74.3</v>
+      </c>
+      <c r="M6" s="3">
+        <v>47.5</v>
+      </c>
+      <c r="N6" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="O6" s="3">
+        <v>46.2</v>
+      </c>
+      <c r="P6" s="3">
+        <v>49.9</v>
+      </c>
+      <c r="Q6" s="3">
+        <v>105.34</v>
+      </c>
+      <c r="R6" s="3">
+        <v>45.1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="3">
+        <v>17</v>
+      </c>
+      <c r="D7" s="3">
+        <v>84</v>
+      </c>
+      <c r="E7" s="3">
+        <v>110.3</v>
+      </c>
+      <c r="F7" s="3">
+        <v>106.3</v>
+      </c>
+      <c r="G7" s="3">
+        <v>4</v>
+      </c>
+      <c r="H7" s="3">
+        <v>77.3</v>
+      </c>
+      <c r="I7" s="3">
+        <v>1.89</v>
+      </c>
+      <c r="J7" s="3">
+        <v>20</v>
+      </c>
+      <c r="K7" s="3">
+        <v>21.3</v>
+      </c>
+      <c r="L7" s="3">
+        <v>64.5</v>
+      </c>
+      <c r="M7" s="3">
+        <v>45.2</v>
+      </c>
+      <c r="N7" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="O7" s="3">
+        <v>53.9</v>
+      </c>
+      <c r="P7" s="3">
+        <v>59.2</v>
+      </c>
+      <c r="Q7" s="3">
+        <v>107.32</v>
+      </c>
+      <c r="R7" s="3">
+        <v>50.9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="3">
+        <v>33</v>
+      </c>
+      <c r="D8" s="3">
+        <v>80</v>
+      </c>
+      <c r="E8" s="3">
+        <v>104.7</v>
+      </c>
+      <c r="F8" s="3">
+        <v>94.4</v>
+      </c>
+      <c r="G8" s="3">
+        <v>10.3</v>
+      </c>
+      <c r="H8" s="3">
+        <v>60.6</v>
+      </c>
+      <c r="I8" s="3">
+        <v>1.48</v>
+      </c>
+      <c r="J8" s="3">
+        <v>17.3</v>
+      </c>
+      <c r="K8" s="3">
+        <v>18.5</v>
+      </c>
+      <c r="L8" s="3">
+        <v>74.400000000000006</v>
+      </c>
+      <c r="M8" s="3">
+        <v>48</v>
+      </c>
+      <c r="N8" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="O8" s="3">
+        <v>58.1</v>
+      </c>
+      <c r="P8" s="3">
+        <v>60.8</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>110.91</v>
+      </c>
+      <c r="R8" s="3">
+        <v>54.3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="3">
+        <v>20</v>
+      </c>
+      <c r="D9" s="3">
+        <v>76</v>
+      </c>
+      <c r="E9" s="3">
+        <v>107.3</v>
+      </c>
+      <c r="F9" s="3">
+        <v>115.2</v>
+      </c>
+      <c r="G9" s="3">
+        <v>-8</v>
+      </c>
+      <c r="H9" s="3">
+        <v>68.8</v>
+      </c>
+      <c r="I9" s="3">
+        <v>1.52</v>
+      </c>
+      <c r="J9" s="3">
+        <v>18.2</v>
+      </c>
+      <c r="K9" s="3">
+        <v>40.700000000000003</v>
+      </c>
+      <c r="L9" s="3">
+        <v>79.7</v>
+      </c>
+      <c r="M9" s="3">
+        <v>59.4</v>
+      </c>
+      <c r="N9" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="O9" s="3">
+        <v>53.5</v>
+      </c>
+      <c r="P9" s="3">
+        <v>56.9</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>104.36</v>
+      </c>
+      <c r="R9" s="3">
+        <v>47.4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="3">
+        <v>15</v>
+      </c>
+      <c r="D10" s="3">
+        <v>62</v>
+      </c>
+      <c r="E10" s="3">
+        <v>111</v>
+      </c>
+      <c r="F10" s="3">
+        <v>95.7</v>
+      </c>
+      <c r="G10" s="3">
+        <v>15.4</v>
+      </c>
+      <c r="H10" s="3">
+        <v>63</v>
+      </c>
+      <c r="I10" s="3">
+        <v>1.48</v>
+      </c>
+      <c r="J10" s="3">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="K10" s="3">
+        <v>30.5</v>
+      </c>
+      <c r="L10" s="3">
+        <v>78.599999999999994</v>
+      </c>
+      <c r="M10" s="3">
+        <v>56.6</v>
+      </c>
+      <c r="N10" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="O10" s="3">
+        <v>58.3</v>
+      </c>
+      <c r="P10" s="3">
+        <v>61.3</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>106.37</v>
+      </c>
+      <c r="R10" s="3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A11" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="3">
+        <v>20</v>
+      </c>
+      <c r="D11" s="3">
+        <v>56</v>
+      </c>
+      <c r="E11" s="3">
+        <v>105.1</v>
+      </c>
+      <c r="F11" s="3">
+        <v>126.4</v>
+      </c>
+      <c r="G11" s="3">
+        <v>-21.3</v>
+      </c>
+      <c r="H11" s="3">
+        <v>52</v>
+      </c>
+      <c r="I11" s="3">
+        <v>1.63</v>
+      </c>
+      <c r="J11" s="3">
+        <v>16.8</v>
+      </c>
+      <c r="K11" s="3">
+        <v>24</v>
+      </c>
+      <c r="L11" s="3">
+        <v>65.3</v>
+      </c>
+      <c r="M11" s="3">
+        <v>44.4</v>
+      </c>
+      <c r="N11" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="O11" s="3">
+        <v>55.6</v>
+      </c>
+      <c r="P11" s="3">
+        <v>57.8</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>102.53</v>
+      </c>
+      <c r="R11" s="3">
+        <v>42.3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="3">
+        <v>25</v>
+      </c>
+      <c r="D12" s="3">
+        <v>40</v>
+      </c>
+      <c r="E12" s="3">
+        <v>109.3</v>
+      </c>
+      <c r="F12" s="3">
+        <v>96</v>
+      </c>
+      <c r="G12" s="3">
+        <v>13.3</v>
+      </c>
+      <c r="H12" s="3">
+        <v>62.5</v>
+      </c>
+      <c r="I12" s="3">
+        <v>1.39</v>
+      </c>
+      <c r="J12" s="3">
+        <v>19.399999999999999</v>
+      </c>
+      <c r="K12" s="3">
+        <v>20.6</v>
+      </c>
+      <c r="L12" s="3">
+        <v>84.6</v>
+      </c>
+      <c r="M12" s="3">
+        <v>54.8</v>
+      </c>
+      <c r="N12" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="O12" s="3">
+        <v>63.9</v>
+      </c>
+      <c r="P12" s="3">
+        <v>65.599999999999994</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>117.6</v>
+      </c>
+      <c r="R12" s="3">
+        <v>53.8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A13" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="3">
+        <v>15</v>
+      </c>
+      <c r="D13" s="3">
+        <v>35</v>
+      </c>
+      <c r="E13" s="3">
+        <v>113.9</v>
+      </c>
+      <c r="F13" s="3">
+        <v>83.8</v>
+      </c>
+      <c r="G13" s="3">
+        <v>30.2</v>
+      </c>
+      <c r="H13" s="3">
+        <v>61.1</v>
+      </c>
+      <c r="I13" s="3">
+        <v>2</v>
+      </c>
+      <c r="J13" s="3">
+        <v>20</v>
+      </c>
+      <c r="K13" s="3">
+        <v>27.3</v>
+      </c>
+      <c r="L13" s="3">
+        <v>72.7</v>
+      </c>
+      <c r="M13" s="3">
+        <v>53.2</v>
+      </c>
+      <c r="N13" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="O13" s="3">
+        <v>62.7</v>
+      </c>
+      <c r="P13" s="3">
+        <v>63.4</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>110.13</v>
+      </c>
+      <c r="R13" s="3">
+        <v>65.400000000000006</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" display="https://www.nba.com/team/1610612765/traditional" xr:uid="{62FCF1C8-87FA-A340-8E05-A873AE804010}"/>
+    <hyperlink ref="B3" r:id="rId2" display="https://www.nba.com/team/1610612765/traditional" xr:uid="{DD5CDCA1-B4B0-E149-A7A8-4CEE1F3189E0}"/>
+    <hyperlink ref="B4" r:id="rId3" display="https://www.nba.com/team/1610612765/traditional" xr:uid="{1B398DAC-9BC3-7249-8764-1B5D7F549C54}"/>
+    <hyperlink ref="B5" r:id="rId4" display="https://www.nba.com/team/1610612765/traditional" xr:uid="{F74B4FC1-E52B-B54A-A649-5F63A5A2A849}"/>
+    <hyperlink ref="B6" r:id="rId5" display="https://www.nba.com/team/1610612765/traditional" xr:uid="{65FD9ED1-A661-E047-8FAA-83913A137127}"/>
+    <hyperlink ref="B7" r:id="rId6" display="https://www.nba.com/team/1610612765/traditional" xr:uid="{525F691C-24BA-874C-9FB1-F7381D6411F0}"/>
+    <hyperlink ref="B8" r:id="rId7" display="https://www.nba.com/team/1610612765/traditional" xr:uid="{DA59F28C-0B8D-9F49-A472-6ABD1E0D3B33}"/>
+    <hyperlink ref="B9" r:id="rId8" display="https://www.nba.com/team/1610612765/traditional" xr:uid="{68E3E994-B0D8-F54F-AC41-0FA3375D6CC9}"/>
+    <hyperlink ref="B10" r:id="rId9" display="https://www.nba.com/team/1610612765/traditional" xr:uid="{B3AC5B63-8868-A64A-AA06-BE426555B5B6}"/>
+    <hyperlink ref="B11" r:id="rId10" display="https://www.nba.com/team/1610612765/traditional" xr:uid="{0E062AA5-7271-C443-A73C-082A2398D56C}"/>
+    <hyperlink ref="B12" r:id="rId11" display="https://www.nba.com/team/1610612765/traditional" xr:uid="{2DA7F9E1-32AC-864D-8FE6-7F3EDCFF0603}"/>
+    <hyperlink ref="B13" r:id="rId12" display="https://www.nba.com/team/1610612765/traditional" xr:uid="{E983B87D-E8DD-3C4B-8391-FB2A191DA713}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA002376-47A3-F24B-98F6-9704C8E7C6EA}">
+  <dimension ref="A1:S13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="65.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="3">
+        <v>39</v>
+      </c>
+      <c r="D2" s="3">
+        <v>12.6</v>
+      </c>
+      <c r="E2" s="3">
+        <v>72.099999999999994</v>
+      </c>
+      <c r="F2" s="3">
+        <v>27.9</v>
+      </c>
+      <c r="G2" s="3">
+        <v>64.599999999999994</v>
+      </c>
+      <c r="H2" s="3">
+        <v>7.2</v>
+      </c>
+      <c r="I2" s="3">
+        <v>23.2</v>
+      </c>
+      <c r="J2" s="3">
+        <v>19.100000000000001</v>
+      </c>
+      <c r="K2" s="3">
+        <v>12.2</v>
+      </c>
+      <c r="L2" s="3">
+        <v>15.6</v>
+      </c>
+      <c r="M2" s="3">
+        <v>57.4</v>
+      </c>
+      <c r="N2" s="3">
+        <v>54.2</v>
+      </c>
+      <c r="O2" s="3">
+        <v>45.8</v>
+      </c>
+      <c r="P2" s="3">
+        <v>80.900000000000006</v>
+      </c>
+      <c r="Q2" s="3">
+        <v>19.100000000000001</v>
+      </c>
+      <c r="R2" s="3">
+        <v>59.3</v>
+      </c>
+      <c r="S2" s="3">
+        <v>40.700000000000003</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="3">
+        <v>21</v>
+      </c>
+      <c r="D3" s="3">
+        <v>12.4</v>
+      </c>
+      <c r="E3" s="3">
+        <v>60.9</v>
+      </c>
+      <c r="F3" s="3">
+        <v>39.1</v>
+      </c>
+      <c r="G3" s="3">
+        <v>51.3</v>
+      </c>
+      <c r="H3" s="3">
+        <v>5</v>
+      </c>
+      <c r="I3" s="3">
+        <v>37.299999999999997</v>
+      </c>
+      <c r="J3" s="3">
+        <v>16.2</v>
+      </c>
+      <c r="K3" s="3">
+        <v>11.3</v>
+      </c>
+      <c r="L3" s="3">
+        <v>13.2</v>
+      </c>
+      <c r="M3" s="3">
+        <v>46.3</v>
+      </c>
+      <c r="N3" s="3">
+        <v>54</v>
+      </c>
+      <c r="O3" s="3">
+        <v>46</v>
+      </c>
+      <c r="P3" s="3">
+        <v>88.6</v>
+      </c>
+      <c r="Q3" s="3">
+        <v>11.4</v>
+      </c>
+      <c r="R3" s="3">
+        <v>65.3</v>
+      </c>
+      <c r="S3" s="3">
+        <v>34.700000000000003</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="3">
+        <v>17</v>
+      </c>
+      <c r="D4" s="3">
+        <v>5</v>
+      </c>
+      <c r="E4" s="3">
+        <v>53.3</v>
+      </c>
+      <c r="F4" s="3">
+        <v>46.7</v>
+      </c>
+      <c r="G4" s="3">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="H4" s="3">
+        <v>2</v>
+      </c>
+      <c r="I4" s="3">
+        <v>47.1</v>
+      </c>
+      <c r="J4" s="3">
+        <v>15.7</v>
+      </c>
+      <c r="K4" s="3">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="L4" s="3">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="M4" s="3">
+        <v>31.4</v>
+      </c>
+      <c r="N4" s="3">
+        <v>58.8</v>
+      </c>
+      <c r="O4" s="3">
+        <v>41.2</v>
+      </c>
+      <c r="P4" s="3">
+        <v>96.9</v>
+      </c>
+      <c r="Q4" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="R4" s="3">
+        <v>77.3</v>
+      </c>
+      <c r="S4" s="3">
+        <v>22.7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="3">
+        <v>25</v>
+      </c>
+      <c r="D5" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="E5" s="3">
+        <v>48.1</v>
+      </c>
+      <c r="F5" s="3">
+        <v>51.9</v>
+      </c>
+      <c r="G5" s="3">
+        <v>32.4</v>
+      </c>
+      <c r="H5" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="I5" s="3">
+        <v>55.9</v>
+      </c>
+      <c r="J5" s="3">
+        <v>13</v>
+      </c>
+      <c r="K5" s="3">
+        <v>11.7</v>
+      </c>
+      <c r="L5" s="3">
+        <v>13</v>
+      </c>
+      <c r="M5" s="3">
+        <v>29.1</v>
+      </c>
+      <c r="N5" s="3">
+        <v>57.5</v>
+      </c>
+      <c r="O5" s="3">
+        <v>42.5</v>
+      </c>
+      <c r="P5" s="3">
+        <v>84.8</v>
+      </c>
+      <c r="Q5" s="3">
+        <v>15.2</v>
+      </c>
+      <c r="R5" s="3">
+        <v>72.099999999999994</v>
+      </c>
+      <c r="S5" s="3">
+        <v>27.9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="3">
+        <v>15</v>
+      </c>
+      <c r="D6" s="3">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="E6" s="3">
+        <v>57.8</v>
+      </c>
+      <c r="F6" s="3">
+        <v>42.2</v>
+      </c>
+      <c r="G6" s="3">
+        <v>46.4</v>
+      </c>
+      <c r="H6" s="3">
+        <v>2.6</v>
+      </c>
+      <c r="I6" s="3">
+        <v>37.700000000000003</v>
+      </c>
+      <c r="J6" s="3">
+        <v>11.3</v>
+      </c>
+      <c r="K6" s="3">
+        <v>15.9</v>
+      </c>
+      <c r="L6" s="3">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="M6" s="3">
+        <v>43.7</v>
+      </c>
+      <c r="N6" s="3">
+        <v>48.6</v>
+      </c>
+      <c r="O6" s="3">
+        <v>51.4</v>
+      </c>
+      <c r="P6" s="3">
+        <v>89.5</v>
+      </c>
+      <c r="Q6" s="3">
+        <v>10.5</v>
+      </c>
+      <c r="R6" s="3">
+        <v>63</v>
+      </c>
+      <c r="S6" s="3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="3">
+        <v>50</v>
+      </c>
+      <c r="D7" s="3">
+        <v>4</v>
+      </c>
+      <c r="E7" s="3">
+        <v>62.7</v>
+      </c>
+      <c r="F7" s="3">
+        <v>37.299999999999997</v>
+      </c>
+      <c r="G7" s="3">
+        <v>51.8</v>
+      </c>
+      <c r="H7" s="3">
+        <v>7.5</v>
+      </c>
+      <c r="I7" s="3">
+        <v>28.8</v>
+      </c>
+      <c r="J7" s="3">
+        <v>10</v>
+      </c>
+      <c r="K7" s="3">
+        <v>19.399999999999999</v>
+      </c>
+      <c r="L7" s="3">
+        <v>15.1</v>
+      </c>
+      <c r="M7" s="3">
+        <v>44.3</v>
+      </c>
+      <c r="N7" s="3">
+        <v>47.7</v>
+      </c>
+      <c r="O7" s="3">
+        <v>52.3</v>
+      </c>
+      <c r="P7" s="3">
+        <v>91.8</v>
+      </c>
+      <c r="Q7" s="3">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="R7" s="3">
+        <v>59.7</v>
+      </c>
+      <c r="S7" s="3">
+        <v>40.299999999999997</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="3">
+        <v>20</v>
+      </c>
+      <c r="D8" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="E8" s="3">
+        <v>54.9</v>
+      </c>
+      <c r="F8" s="3">
+        <v>45.1</v>
+      </c>
+      <c r="G8" s="3">
+        <v>42.9</v>
+      </c>
+      <c r="H8" s="3">
+        <v>5.6</v>
+      </c>
+      <c r="I8" s="3">
+        <v>44.1</v>
+      </c>
+      <c r="J8" s="3">
+        <v>9.6</v>
+      </c>
+      <c r="K8" s="3">
+        <v>13</v>
+      </c>
+      <c r="L8" s="3">
+        <v>7.3</v>
+      </c>
+      <c r="M8" s="3">
+        <v>37.299999999999997</v>
+      </c>
+      <c r="N8" s="3">
+        <v>57.9</v>
+      </c>
+      <c r="O8" s="3">
+        <v>42.1</v>
+      </c>
+      <c r="P8" s="3">
+        <v>84.6</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>15.4</v>
+      </c>
+      <c r="R8" s="3">
+        <v>68.8</v>
+      </c>
+      <c r="S8" s="3">
+        <v>31.3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="3">
+        <v>28</v>
+      </c>
+      <c r="D9" s="3">
+        <v>3.3</v>
+      </c>
+      <c r="E9" s="3">
+        <v>53.5</v>
+      </c>
+      <c r="F9" s="3">
+        <v>46.5</v>
+      </c>
+      <c r="G9" s="3">
+        <v>41.8</v>
+      </c>
+      <c r="H9" s="3">
+        <v>5</v>
+      </c>
+      <c r="I9" s="3">
+        <v>43.3</v>
+      </c>
+      <c r="J9" s="3">
+        <v>20.9</v>
+      </c>
+      <c r="K9" s="3">
+        <v>14.9</v>
+      </c>
+      <c r="L9" s="3">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="M9" s="3">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="N9" s="3">
+        <v>42.9</v>
+      </c>
+      <c r="O9" s="3">
+        <v>57.1</v>
+      </c>
+      <c r="P9" s="3">
+        <v>93.1</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>6.9</v>
+      </c>
+      <c r="R9" s="3">
+        <v>63.4</v>
+      </c>
+      <c r="S9" s="3">
+        <v>36.6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="3">
+        <v>20</v>
+      </c>
+      <c r="D10" s="3">
+        <v>2.8</v>
+      </c>
+      <c r="E10" s="3">
+        <v>71.7</v>
+      </c>
+      <c r="F10" s="3">
+        <v>28.3</v>
+      </c>
+      <c r="G10" s="3">
+        <v>65</v>
+      </c>
+      <c r="H10" s="3">
+        <v>3.3</v>
+      </c>
+      <c r="I10" s="3">
+        <v>24.4</v>
+      </c>
+      <c r="J10" s="3">
+        <v>11.4</v>
+      </c>
+      <c r="K10" s="3">
+        <v>10.6</v>
+      </c>
+      <c r="L10" s="3">
+        <v>21.1</v>
+      </c>
+      <c r="M10" s="3">
+        <v>61.8</v>
+      </c>
+      <c r="N10" s="3">
+        <v>45</v>
+      </c>
+      <c r="O10" s="3">
+        <v>55</v>
+      </c>
+      <c r="P10" s="3">
+        <v>80</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>20</v>
+      </c>
+      <c r="R10" s="3">
+        <v>52</v>
+      </c>
+      <c r="S10" s="3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A11" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="3">
+        <v>33</v>
+      </c>
+      <c r="D11" s="3">
+        <v>2.4</v>
+      </c>
+      <c r="E11" s="3">
+        <v>49</v>
+      </c>
+      <c r="F11" s="3">
+        <v>51</v>
+      </c>
+      <c r="G11" s="3">
+        <v>40</v>
+      </c>
+      <c r="H11" s="3">
+        <v>5</v>
+      </c>
+      <c r="I11" s="3">
+        <v>46.5</v>
+      </c>
+      <c r="J11" s="3">
+        <v>14</v>
+      </c>
+      <c r="K11" s="3">
+        <v>13.5</v>
+      </c>
+      <c r="L11" s="3">
+        <v>18</v>
+      </c>
+      <c r="M11" s="3">
+        <v>35</v>
+      </c>
+      <c r="N11" s="3">
+        <v>40</v>
+      </c>
+      <c r="O11" s="3">
+        <v>60</v>
+      </c>
+      <c r="P11" s="3">
+        <v>87.1</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>12.9</v>
+      </c>
+      <c r="R11" s="3">
+        <v>60.6</v>
+      </c>
+      <c r="S11" s="3">
+        <v>39.4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="3">
+        <v>15</v>
+      </c>
+      <c r="D12" s="3">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="E12" s="3">
+        <v>56.7</v>
+      </c>
+      <c r="F12" s="3">
+        <v>43.3</v>
+      </c>
+      <c r="G12" s="3">
+        <v>53.3</v>
+      </c>
+      <c r="H12" s="3">
+        <v>11.1</v>
+      </c>
+      <c r="I12" s="3">
+        <v>40</v>
+      </c>
+      <c r="J12" s="3">
+        <v>16.7</v>
+      </c>
+      <c r="K12" s="3">
+        <v>6.7</v>
+      </c>
+      <c r="L12" s="3">
+        <v>20</v>
+      </c>
+      <c r="M12" s="3">
+        <v>42.2</v>
+      </c>
+      <c r="N12" s="3">
+        <v>54.2</v>
+      </c>
+      <c r="O12" s="3">
+        <v>45.8</v>
+      </c>
+      <c r="P12" s="3">
+        <v>75</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>25</v>
+      </c>
+      <c r="R12" s="3">
+        <v>61.1</v>
+      </c>
+      <c r="S12" s="3">
+        <v>38.9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A13" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="3">
+        <v>25</v>
+      </c>
+      <c r="D13" s="3">
+        <v>1.6</v>
+      </c>
+      <c r="E13" s="3">
+        <v>58.3</v>
+      </c>
+      <c r="F13" s="3">
+        <v>41.7</v>
+      </c>
+      <c r="G13" s="3">
+        <v>52.8</v>
+      </c>
+      <c r="H13" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="I13" s="3">
+        <v>34</v>
+      </c>
+      <c r="J13" s="3">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="K13" s="3">
+        <v>13.2</v>
+      </c>
+      <c r="L13" s="3">
+        <v>9.4</v>
+      </c>
+      <c r="M13" s="3">
+        <v>49.1</v>
+      </c>
+      <c r="N13" s="3">
+        <v>50</v>
+      </c>
+      <c r="O13" s="3">
+        <v>50</v>
+      </c>
+      <c r="P13" s="3">
+        <v>91.7</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="R13" s="3">
+        <v>62.5</v>
+      </c>
+      <c r="S13" s="3">
+        <v>37.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" display="https://www.nba.com/team/1610612765/traditional" xr:uid="{738DDB53-CBED-9743-AB59-6BA770A8C38F}"/>
+    <hyperlink ref="B3" r:id="rId2" display="https://www.nba.com/team/1610612765/traditional" xr:uid="{6D9D5B92-0ADC-9E4E-9599-D6A163E7DBC4}"/>
+    <hyperlink ref="B4" r:id="rId3" display="https://www.nba.com/team/1610612765/traditional" xr:uid="{F16AC554-3108-5A4D-A51C-09C50CEB7F62}"/>
+    <hyperlink ref="B5" r:id="rId4" display="https://www.nba.com/team/1610612765/traditional" xr:uid="{E91EE63C-F7F3-E84B-9033-6596121B777A}"/>
+    <hyperlink ref="B6" r:id="rId5" display="https://www.nba.com/team/1610612765/traditional" xr:uid="{85936ADF-7A58-7C4C-B95F-C25DDA8523C3}"/>
+    <hyperlink ref="B7" r:id="rId6" display="https://www.nba.com/team/1610612765/traditional" xr:uid="{65AF82D2-C59F-D942-9B42-CF1D4B9ECF38}"/>
+    <hyperlink ref="B8" r:id="rId7" display="https://www.nba.com/team/1610612765/traditional" xr:uid="{F34B4D15-EA06-894E-87C9-D2D90ABC48C5}"/>
+    <hyperlink ref="B9" r:id="rId8" display="https://www.nba.com/team/1610612765/traditional" xr:uid="{2ACF59A5-0ACB-0246-8198-8608B76075A6}"/>
+    <hyperlink ref="B10" r:id="rId9" display="https://www.nba.com/team/1610612765/traditional" xr:uid="{8462A05B-A7CC-2E4F-BBB9-2B8EF396A4AA}"/>
+    <hyperlink ref="B11" r:id="rId10" display="https://www.nba.com/team/1610612765/traditional" xr:uid="{D886B85B-1A49-EA4E-B1BF-FC83E973DE6E}"/>
+    <hyperlink ref="B12" r:id="rId11" display="https://www.nba.com/team/1610612765/traditional" xr:uid="{A5B8481B-E474-4541-8008-A1A82C876B00}"/>
+    <hyperlink ref="B13" r:id="rId12" display="https://www.nba.com/team/1610612765/traditional" xr:uid="{926AC0EF-E276-C644-A6DB-E77E38B1477E}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E665C6A7-E821-364A-83FF-DBFEAA5B4B34}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Projects/Pistons-Lineup-Data-2024-25.xlsx
+++ b/Projects/Pistons-Lineup-Data-2024-25.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thejjserg/Documents/GitHub/basketball-analytics/Projects/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D298B982-8C46-6342-B714-5BCFC48F96C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{548D53E7-CA0E-6E4B-90CC-0F36EE6AB630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17680" activeTab="6" xr2:uid="{8C050E1C-C5BA-9F4C-A171-8E53342E2AE2}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17680" xr2:uid="{8C050E1C-C5BA-9F4C-A171-8E53342E2AE2}"/>
   </bookViews>
   <sheets>
     <sheet name="2-Player All Games Traditional" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="5-Player All Games Scoring" sheetId="5" r:id="rId6"/>
     <sheet name="Resources" sheetId="8" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -642,14 +642,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -989,25 +987,27 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="32" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="32" customWidth="1"/>
-    <col min="6" max="6" width="6.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="5.83203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="5.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.83203125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.83203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.83203125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="5.1640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.83203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.1640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="5.83203125" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="7" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="5.1640625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="4.83203125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.83203125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="5.83203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="5.83203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="7" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="6.83203125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="5.83203125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="5.33203125" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="5.1640625" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="5.33203125" bestFit="1" customWidth="1"/>
   </cols>
@@ -11004,20 +11004,21 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="32" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="32" customWidth="1"/>
-    <col min="4" max="5" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.83203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.83203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="7.83203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="8.83203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="7.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.83203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.83203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.1640625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="5.83203125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="8.1640625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="5.83203125" bestFit="1" customWidth="1"/>
@@ -16025,7 +16026,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="32" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="32" customWidth="1"/>
+    <col min="2" max="3" width="15.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.83203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="4" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="5.83203125" bestFit="1" customWidth="1"/>
@@ -16046,7 +16047,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -16055,13 +16056,13 @@
       <c r="C1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G1" s="2" t="s">
@@ -24886,6 +24887,23 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="65.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.2">
